--- a/Excel/模板.xlsx
+++ b/Excel/模板.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Pisces2026\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
@@ -28,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="32">
   <si>
     <t>索引</t>
   </si>
@@ -73,6 +78,15 @@
 2.字段的父类型为class，struct, ClassStructList, ClassStructArray时,填</t>
   </si>
   <si>
+    <t>当前Sheet的类名</t>
+  </si>
+  <si>
+    <t>类只在当前Sheet有效.其他表也是同一个类名需要告警</t>
+  </si>
+  <si>
+    <t>TextConfig</t>
+  </si>
+  <si>
     <t>内容</t>
   </si>
   <si>
@@ -88,6 +102,12 @@
     <t>奖励道具列表_道具数量</t>
   </si>
   <si>
+    <t>字段名，字段可以重复，但是必须在，第6行标识
+字段名重复的几种情况
+1.分文件，例如文本表的Content字段不同文件存放不同语言
+2.是Array或者List</t>
+  </si>
+  <si>
     <t>Conten</t>
   </si>
   <si>
@@ -100,6 +120,17 @@
     <t>Rewards_Amount</t>
   </si>
   <si>
+    <t>数据类型uint,int,bool,string,float,long,double,array,list
+数组和列表必须是具体类型，示例：int[], List&lt;string&gt;  Consume[], List&lt;RewardData&gt;等</t>
+  </si>
+  <si>
+    <t>表示同名字段的作用，
+1.创建分文件是：CreateFile.后缀，例如：CreateFile.En
+2.自定义类型是：自定义类型.字段名.字段类型
+2.1示例1：Struct.ItemId.int
+2.2示例2：Class.ItemId.int</t>
+  </si>
+  <si>
     <t>CreateFile</t>
   </si>
   <si>
@@ -107,15 +138,6 @@
   </si>
   <si>
     <t>ClassStructList</t>
-  </si>
-  <si>
-    <t>Cn</t>
-  </si>
-  <si>
-    <t>En</t>
-  </si>
-  <si>
-    <t>SingleRewardData</t>
   </si>
 </sst>
 </file>
@@ -757,16 +779,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1095,103 +1117,103 @@
   </cols>
   <sheetData>
     <row r="1" ht="54" customHeight="1" spans="1:17">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
     <row r="2" ht="39" customHeight="1" spans="1:17">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
     </row>
     <row r="3" ht="41" customHeight="1" spans="1:17">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1" t="s">
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
     </row>
     <row r="4" ht="39" customHeight="1" spans="1:17">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1200,19 +1222,19 @@
       <c r="Q4" s="3"/>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:17">
-      <c r="A5" s="1"/>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -1790,183 +1812,208 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="51.125" customWidth="1"/>
-    <col min="2" max="2" width="40.875" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="45.875" customWidth="1"/>
-    <col min="5" max="5" width="43.875" customWidth="1"/>
-    <col min="6" max="6" width="28.5" customWidth="1"/>
-    <col min="7" max="7" width="35.375" customWidth="1"/>
-    <col min="8" max="8" width="36.5" customWidth="1"/>
-    <col min="9" max="9" width="30.25" customWidth="1"/>
-    <col min="10" max="10" width="30.875" customWidth="1"/>
+    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="3" max="3" width="40.875" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="45.875" customWidth="1"/>
+    <col min="6" max="6" width="43.875" customWidth="1"/>
+    <col min="7" max="7" width="28.5" customWidth="1"/>
+    <col min="8" max="8" width="35.375" customWidth="1"/>
+    <col min="9" max="9" width="36.5" customWidth="1"/>
+    <col min="10" max="10" width="30.25" customWidth="1"/>
+    <col min="11" max="11" width="30.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="40" customHeight="1" spans="1:11">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="2" ht="44" customHeight="1" spans="1:11">
+      <c r="A2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" ht="40" customHeight="1" spans="1:11">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1" spans="1:10">
-      <c r="A2" s="1" t="s">
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1" spans="1:10">
-      <c r="A3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="72" customHeight="1" spans="1:11">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1" spans="1:10">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1" spans="1:10">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1" t="s">
+    <row r="6" s="1" customFormat="1" ht="90" customHeight="1" spans="1:11">
+      <c r="A6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" ht="29" customHeight="1"/>
+    <row r="8" ht="27" customHeight="1"/>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3 B3 C3 D3 E3 F3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5 C5:G5">
       <formula1>"uint,int,string,float,double,vector2,vector3,class,struct"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3 H3 I3 J3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:K5">
       <formula1>"uint,int,string,float,double,vector2,vector3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A4 B4 C4 D4 E4 F4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B6 C6:G6">
       <formula1>"CreateFile,Array,List,HashSet"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4 H4 I4 J4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:K6">
       <formula1>"CreateFile,Array,List,Class,Struct,ClassStructList,ClassStructArray"</formula1>
     </dataValidation>
   </dataValidations>
